--- a/data/template.xlsx
+++ b/data/template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b31c4694adffee76/Dropbox/Documentos/Devel/SpeakersDesign/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\devel\SpeakersDesign\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7A8DF13-911C-417D-929F-D0C24BB29F32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDB585B2-2737-446C-8CAF-D34E8BB03CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="640" windowWidth="12860" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,33 +30,7 @@
     <author/>
   </authors>
   <commentList>
-    <comment ref="G2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>Seleccionar tapacantos asociados a la optimizacion
-1= aplica Tapacanto
-2= no aplica</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>Ingresar un Sku Valido que identifique el producto a optimizar.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -68,7 +42,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -81,7 +55,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -94,7 +68,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -103,20 +77,6 @@
             <rFont val="Calibri"/>
           </rPr>
           <t>Descripcion de la pieza</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>Indicador que permite Rotar o no el tablero, según el sentido de la Veta
-Veta Rota Libre=1
-Veta Fija=0</t>
         </r>
       </text>
     </comment>
@@ -130,13 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
-  <si>
-    <t>TAPACANTO</t>
-  </si>
-  <si>
-    <t>SKU</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>CANTIDAD</t>
   </si>
@@ -148,9 +102,6 @@
   </si>
   <si>
     <t>NOMBRE</t>
-  </si>
-  <si>
-    <t>VETA</t>
   </si>
   <si>
     <t>Aiyima 65 Frontal/Trasero</t>
@@ -193,25 +144,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -224,7 +160,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -237,54 +173,8 @@
         <bgColor rgb="FF00316C"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF002060"/>
-        <bgColor rgb="FF002060"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
-        <bgColor rgb="FFD9D9D9"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="13">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -333,122 +223,22 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFFF0000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFFF0000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFFF0000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFF0000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -768,436 +558,214 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O1000"/>
+  <dimension ref="A1:D997"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="3" width="10.54296875" customWidth="1"/>
     <col min="4" max="4" width="27.81640625" customWidth="1"/>
-    <col min="5" max="5" width="10.54296875" customWidth="1"/>
-    <col min="6" max="6" width="3.7265625" customWidth="1"/>
-    <col min="7" max="7" width="4.1796875" customWidth="1"/>
-    <col min="8" max="8" width="2.81640625" customWidth="1"/>
-    <col min="9" max="9" width="3.453125" customWidth="1"/>
-    <col min="10" max="10" width="3.1796875" customWidth="1"/>
-    <col min="11" max="11" width="3.453125" customWidth="1"/>
-    <col min="12" max="12" width="2.54296875" customWidth="1"/>
-    <col min="13" max="13" width="4" customWidth="1"/>
-    <col min="14" max="14" width="3.1796875" customWidth="1"/>
-    <col min="15" max="15" width="10.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
+    <row r="1" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="1"/>
+    <row r="2" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>308</v>
+      </c>
+      <c r="C2">
+        <v>204</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="3" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="6">
-        <v>128314</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
-      <c r="L3" s="21"/>
-      <c r="M3" s="22"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="1"/>
+    <row r="3" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>4</v>
+      </c>
+      <c r="B3">
+        <v>204</v>
+      </c>
+      <c r="C3">
+        <v>214</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="4" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="10" t="s">
+    <row r="4" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4">
         <v>4</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="10" t="s">
+      <c r="B4" s="4">
+        <v>272</v>
+      </c>
+      <c r="C4">
+        <v>214</v>
+      </c>
+      <c r="D4" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="11"/>
-      <c r="G4" s="12"/>
-      <c r="I4" s="13"/>
-      <c r="K4" s="14"/>
-      <c r="M4" s="15"/>
-      <c r="O4" s="1"/>
     </row>
-    <row r="5" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>308</v>
+      <c r="B5" s="4">
+        <v>172</v>
       </c>
       <c r="C5">
-        <v>204</v>
+        <v>120</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="16">
-        <v>0</v>
-      </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="16">
-        <v>0</v>
-      </c>
-      <c r="H5" s="17"/>
-      <c r="I5" s="16">
-        <v>0</v>
-      </c>
-      <c r="J5" s="17"/>
-      <c r="K5" s="16">
-        <v>0</v>
-      </c>
-      <c r="L5" s="17"/>
-      <c r="M5" s="16">
-        <v>0</v>
-      </c>
-      <c r="N5" s="17"/>
     </row>
-    <row r="6" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6">
-        <v>204</v>
+        <v>120</v>
       </c>
       <c r="C6">
-        <v>214</v>
+        <v>107</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="16">
-        <v>0</v>
-      </c>
-      <c r="F6" s="17"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="17"/>
     </row>
-    <row r="7" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>4</v>
       </c>
-      <c r="B7" s="18">
-        <v>272</v>
+      <c r="B7">
+        <v>136</v>
       </c>
       <c r="C7">
-        <v>214</v>
+        <v>107</v>
       </c>
       <c r="D7" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="16">
-        <v>0</v>
-      </c>
-      <c r="F7" s="17"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="17"/>
     </row>
-    <row r="8" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>4</v>
       </c>
-      <c r="B8" s="18">
-        <v>172</v>
+      <c r="B8">
+        <v>224</v>
       </c>
       <c r="C8">
-        <v>120</v>
+        <v>152</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="16">
-        <v>0</v>
-      </c>
-      <c r="F8" s="17"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
     </row>
-    <row r="9" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>4</v>
       </c>
-      <c r="B9">
-        <v>120</v>
+      <c r="B9" s="4">
+        <v>152</v>
       </c>
       <c r="C9">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="16">
-        <v>0</v>
-      </c>
-      <c r="F9" s="17"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="19"/>
-      <c r="N9" s="17"/>
     </row>
-    <row r="10" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>4</v>
       </c>
-      <c r="B10">
-        <v>136</v>
+      <c r="B10" s="4">
+        <v>188</v>
       </c>
       <c r="C10">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="16">
-        <v>0</v>
-      </c>
-      <c r="F10" s="17"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
     </row>
-    <row r="11" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>4</v>
       </c>
       <c r="B11">
-        <v>224</v>
+        <v>324</v>
       </c>
       <c r="C11">
-        <v>152</v>
+        <v>214</v>
       </c>
       <c r="D11" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="16">
-        <v>0</v>
-      </c>
-      <c r="F11" s="17"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
     </row>
-    <row r="12" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>4</v>
       </c>
-      <c r="B12" s="18">
-        <v>152</v>
+      <c r="B12">
+        <v>214</v>
       </c>
       <c r="C12">
-        <v>148</v>
+        <v>226</v>
       </c>
       <c r="D12" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="16">
-        <v>0</v>
-      </c>
-      <c r="F12" s="17"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
     </row>
-    <row r="13" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>4</v>
       </c>
-      <c r="B13" s="18">
-        <v>188</v>
+      <c r="B13">
+        <v>288</v>
       </c>
       <c r="C13">
-        <v>148</v>
+        <v>226</v>
       </c>
       <c r="D13" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="16">
-        <v>0</v>
-      </c>
-      <c r="F13" s="17"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
     </row>
-    <row r="14" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14">
-        <v>4</v>
-      </c>
-      <c r="B14">
-        <v>324</v>
-      </c>
-      <c r="C14">
-        <v>214</v>
-      </c>
-      <c r="D14" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" s="16">
-        <v>0</v>
-      </c>
-      <c r="F14" s="17"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="19"/>
-      <c r="N14" s="17"/>
-    </row>
-    <row r="15" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15">
-        <v>4</v>
-      </c>
-      <c r="B15">
-        <v>214</v>
-      </c>
-      <c r="C15">
-        <v>226</v>
-      </c>
-      <c r="D15" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="16">
-        <v>0</v>
-      </c>
-      <c r="F15" s="17"/>
-      <c r="H15" s="19"/>
-      <c r="J15" s="19"/>
-      <c r="L15" s="19"/>
-      <c r="N15" s="17"/>
-    </row>
-    <row r="16" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16">
-        <v>4</v>
-      </c>
-      <c r="B16">
-        <v>288</v>
-      </c>
-      <c r="C16">
-        <v>226</v>
-      </c>
-      <c r="D16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" s="16">
-        <v>0</v>
-      </c>
-      <c r="F16" s="17"/>
-      <c r="H16" s="19"/>
-      <c r="J16" s="19"/>
-      <c r="L16" s="19"/>
-      <c r="N16" s="17"/>
-    </row>
-    <row r="17" spans="6:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F17" s="17"/>
-      <c r="H17" s="19"/>
-      <c r="J17" s="19"/>
-      <c r="L17" s="19"/>
-      <c r="N17" s="17"/>
-    </row>
-    <row r="18" spans="6:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="6:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="6:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="6:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="22" spans="6:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="23" spans="6:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="24" spans="6:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="6:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="6:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="6:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="6:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="6:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="6:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" spans="6:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="6:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="14" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="15" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="18" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="19" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="20" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="21" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="22" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="23" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="24" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="25" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="26" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="27" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="28" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="29" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="30" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="31" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="32" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="33" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="34" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="35" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -1383,9 +951,9 @@
     <row r="215" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="216" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="217" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="218" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="219" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="220" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -2163,14 +1731,7 @@
     <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="G2:M2"/>
-    <mergeCell ref="G3:M3"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <drawing r:id="rId1"/>
